--- a/contenido/datos/dmt_rasch.xlsx
+++ b/contenido/datos/dmt_rasch.xlsx
@@ -510,7 +510,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.902050970438843</v>
+        <v>0.902050970438842</v>
       </c>
       <c r="C2" t="n">
         <v>0.0475170661901236</v>
@@ -557,7 +557,7 @@
         <v>-1.50179789832787</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0529298036230691</v>
+        <v>0.052929803623069</v>
       </c>
     </row>
     <row r="7">
@@ -565,7 +565,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>0.23508804485825</v>
+        <v>0.235088044858249</v>
       </c>
       <c r="C7" t="n">
         <v>0.0448085951542595</v>
@@ -609,7 +609,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.956944426907411</v>
+        <v>-0.956944426907412</v>
       </c>
       <c r="C11" t="n">
         <v>0.0478527028733736</v>
@@ -631,7 +631,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0900565312517703</v>
+        <v>-0.0900565312517707</v>
       </c>
       <c r="C13" t="n">
         <v>0.0446392631021625</v>
@@ -675,7 +675,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>0.245130796880272</v>
+        <v>0.245130796880271</v>
       </c>
       <c r="C17" t="n">
         <v>0.0448255322649262</v>
@@ -730,7 +730,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.579451147412208</v>
+        <v>-0.579451147412209</v>
       </c>
       <c r="C22" t="n">
         <v>0.0457763418035526</v>
@@ -785,7 +785,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>0.429598281703303</v>
+        <v>0.429598281703302</v>
       </c>
       <c r="C27" t="n">
         <v>0.0452630749812321</v>
@@ -818,7 +818,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.282218441821609</v>
+        <v>-0.28221844182161</v>
       </c>
       <c r="C30" t="n">
         <v>0.0448841515846817</v>
@@ -884,7 +884,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>0.0692210082572536</v>
+        <v>0.0692210082572527</v>
       </c>
       <c r="C36" t="n">
         <v>0.0446305713868163</v>
@@ -928,7 +928,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.000458412922875762</v>
+        <v>-0.000458412922876222</v>
       </c>
       <c r="C40" t="n">
         <v>0.0446127549931415</v>
@@ -1052,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.900587649926527</v>
+        <v>0.900587649920779</v>
       </c>
     </row>
     <row r="3">
@@ -1063,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.516799142673404</v>
+        <v>0.516799142651639</v>
       </c>
     </row>
     <row r="4">
@@ -1074,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0120416862635021</v>
+        <v>0.0120416862361248</v>
       </c>
     </row>
     <row r="5">
@@ -1085,7 +1085,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.731807123657939</v>
+        <v>-0.731807123672305</v>
       </c>
     </row>
     <row r="6">
@@ -1096,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.50314788940766</v>
+        <v>-1.50314788933231</v>
       </c>
     </row>
     <row r="7">
@@ -1107,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.233645928598611</v>
+        <v>0.233645928572183</v>
       </c>
     </row>
     <row r="8">
@@ -1118,7 +1118,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1.53223141330999</v>
+        <v>1.53223141340364</v>
       </c>
     </row>
     <row r="9">
@@ -1129,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.11540311276382</v>
+        <v>-0.11540311279076</v>
       </c>
     </row>
     <row r="10">
@@ -1140,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.189297949991826</v>
+        <v>-0.189297950018185</v>
       </c>
     </row>
     <row r="11">
@@ -1151,7 +1151,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.958325719186571</v>
+        <v>-0.958325719188901</v>
       </c>
     </row>
     <row r="12">
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.366928566928411</v>
+        <v>0.366928566903671</v>
       </c>
     </row>
     <row r="13">
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0914837702178214</v>
+        <v>-0.0914837702448973</v>
       </c>
     </row>
     <row r="14">
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.03944661644366</v>
+        <v>-1.03944661643904</v>
       </c>
     </row>
     <row r="15">
@@ -1195,7 +1195,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.161540815233139</v>
+        <v>0.161540815206157</v>
       </c>
     </row>
     <row r="16">
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.17953754383302</v>
+        <v>0.179537543806154</v>
       </c>
     </row>
     <row r="17">
@@ -1217,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.243688256377041</v>
+        <v>0.243688256350709</v>
       </c>
     </row>
     <row r="18">
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.798142382026497</v>
+        <v>0.798142382014572</v>
       </c>
     </row>
     <row r="19">
@@ -1239,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.161540815233139</v>
+        <v>0.161540815206157</v>
       </c>
     </row>
     <row r="20">
@@ -1250,7 +1250,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.35661855163423</v>
+        <v>-1.35661855158337</v>
       </c>
     </row>
     <row r="21">
@@ -1261,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.19844939357249</v>
+        <v>-1.19844939354825</v>
       </c>
     </row>
     <row r="22">
@@ -1272,7 +1272,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.580853178622112</v>
+        <v>-0.580853178641299</v>
       </c>
     </row>
     <row r="23">
@@ -1283,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.79722649198871</v>
+        <v>-1.79722649191922</v>
       </c>
     </row>
     <row r="24">
@@ -1294,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.446609359266024</v>
+        <v>0.446609359242715</v>
       </c>
     </row>
     <row r="25">
@@ -1305,7 +1305,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>-1.73364623523855</v>
+        <v>-1.73364623515716</v>
       </c>
     </row>
     <row r="26">
@@ -1316,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>-2.43885325728436</v>
+        <v>-2.43885325755612</v>
       </c>
     </row>
     <row r="27">
@@ -1327,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.428148445620927</v>
+        <v>0.428148445597258</v>
       </c>
     </row>
     <row r="28">
@@ -1338,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>-2.12977568249211</v>
+        <v>-2.12977568259677</v>
       </c>
     </row>
     <row r="29">
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.37099574271729</v>
+        <v>0.370995742692612</v>
       </c>
     </row>
     <row r="30">
@@ -1360,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.283636107303217</v>
+        <v>-0.283636107328481</v>
       </c>
     </row>
     <row r="31">
@@ -1371,7 +1371,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.223347617667636</v>
+        <v>-0.223347617693646</v>
       </c>
     </row>
     <row r="32">
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.691781050326244</v>
+        <v>0.691781050309709</v>
       </c>
     </row>
     <row r="33">
@@ -1393,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.836764167661582</v>
+        <v>-0.836764167671393</v>
       </c>
     </row>
     <row r="34">
@@ -1404,7 +1404,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.265519537143953</v>
+        <v>-0.265519537169458</v>
       </c>
     </row>
     <row r="35">
@@ -1415,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0339365139482016</v>
+        <v>0.0339365139208193</v>
       </c>
     </row>
     <row r="36">
@@ -1426,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0677862325830179</v>
+        <v>0.0677862325556736</v>
       </c>
     </row>
     <row r="37">
@@ -1437,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.622921947560369</v>
+        <v>-0.62292194757836</v>
       </c>
     </row>
     <row r="38">
@@ -1448,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0.257760613312715</v>
+        <v>0.257760613286529</v>
       </c>
     </row>
     <row r="39">
@@ -1459,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.733967580292443</v>
+        <v>-0.733967580306727</v>
       </c>
     </row>
     <row r="40">
@@ -1470,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.00188994239062844</v>
+        <v>-0.00188994241799067</v>
       </c>
     </row>
     <row r="41">
@@ -1481,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.678124724398917</v>
+        <v>-0.678124724415178</v>
       </c>
     </row>
     <row r="42">
@@ -1492,7 +1492,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.92081009923973</v>
+        <v>-1.92081009921488</v>
       </c>
     </row>
     <row r="43">
@@ -1503,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.865666027492742</v>
+        <v>-0.865666027501032</v>
       </c>
     </row>
     <row r="44">
@@ -1514,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.6872776769739</v>
+        <v>-1.68727767688819</v>
       </c>
     </row>
     <row r="45">
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.16888678824873</v>
+        <v>-1.16888678822877</v>
       </c>
     </row>
     <row r="46">
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.14691593223164</v>
+        <v>-1.14691593221467</v>
       </c>
     </row>
     <row r="47">
@@ -1547,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.856749972861335</v>
+        <v>-0.856749972870109</v>
       </c>
     </row>
     <row r="48">
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>-1.1420562668105</v>
+        <v>-1.14205626679417</v>
       </c>
     </row>
   </sheetData>
